--- a/data/statement.xlsx
+++ b/data/statement.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,19 +495,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Humana PPO</t>
+          <t>Aetna MAPD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P-1004</t>
+          <t>P-1012</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -518,32 +518,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P-1005</t>
+          <t>P-1004</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UnitedHealth HMO</t>
+          <t>Humana PPO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P-1006</t>
+          <t>P-1005</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -554,32 +554,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P-1007</t>
+          <t>P-1006</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cigna PDP</t>
+          <t>UnitedHealth HMO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P-1008</t>
+          <t>P-1007</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -590,32 +590,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P-1009</t>
+          <t>P-1008</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BlueCross Medigap</t>
+          <t>Cigna PDP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P-1010</t>
+          <t>P-1009</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -626,31 +626,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P-1011</t>
+          <t>P-1010</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>BlueCross Medigap</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P-1011</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>450</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Delta Dental</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>P-9999</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>999</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D14" t="n">
         <v>4</v>
       </c>
     </row>
